--- a/catalogue print et signalétique.xlsx
+++ b/catalogue print et signalétique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F908CD1B-2E6B-474A-9DC3-2DA223F1B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267CA51A-59E8-4065-8B6B-782384DB9E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="86">
   <si>
     <t>Colonne A</t>
   </si>
@@ -69,30 +69,6 @@
   </si>
   <si>
     <t>Modèle / Référence exacte</t>
-  </si>
-  <si>
-    <r>
-      <t>100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(ou palier)</t>
-    </r>
   </si>
   <si>
     <t>Panneaux de chantier
@@ -450,7 +426,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -837,7 +813,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -857,8 +833,8 @@
       <c r="H2" s="1">
         <v>50</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
+      <c r="I2" s="1">
+        <v>100</v>
       </c>
       <c r="J2" s="1">
         <v>250</v>
@@ -881,10 +857,10 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3">
@@ -907,13 +883,14 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
@@ -936,13 +913,14 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5">
@@ -965,13 +943,14 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6">
@@ -994,13 +973,14 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7">
@@ -1023,13 +1003,14 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8">
@@ -1052,13 +1033,14 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
       <c r="D9">
         <v>64.8</v>
@@ -1073,13 +1055,14 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>93.6</v>
@@ -1094,13 +1077,14 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>96</v>
@@ -1115,13 +1099,14 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>141.6</v>
@@ -1136,13 +1121,14 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1174,10 +1160,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1208,10 +1194,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1242,10 +1228,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1276,10 +1262,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1310,10 +1296,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1344,10 +1330,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1378,10 +1364,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1412,10 +1398,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1446,10 +1432,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1480,10 +1466,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1514,10 +1500,10 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1548,10 +1534,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1582,10 +1568,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1616,10 +1602,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1650,10 +1636,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1684,10 +1670,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1718,10 +1704,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1752,10 +1738,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1786,10 +1772,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1820,13 +1806,13 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1857,13 +1843,13 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1894,13 +1880,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1931,13 +1917,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1968,13 +1954,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2005,13 +1991,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2042,13 +2028,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2079,13 +2065,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2116,13 +2102,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2153,13 +2139,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2190,13 +2176,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2227,13 +2213,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2264,13 +2250,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2301,13 +2287,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2338,13 +2324,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2375,10 +2361,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2407,10 +2393,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
         <v>47</v>
-      </c>
-      <c r="B49" t="s">
-        <v>48</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2439,10 +2425,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2471,10 +2457,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
         <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>51</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2511,10 +2497,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2551,10 +2537,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2591,10 +2577,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
         <v>54</v>
-      </c>
-      <c r="B54" t="s">
-        <v>55</v>
       </c>
       <c r="D54">
         <v>31.680000000000003</v>
@@ -2631,10 +2617,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55">
         <v>61.600000000000009</v>
@@ -2671,10 +2657,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D56">
         <v>46.2</v>
@@ -2707,10 +2693,10 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57">
         <v>31.680000000000003</v>
@@ -2747,10 +2733,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58">
         <v>70.400000000000006</v>
@@ -2785,10 +2771,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D59">
         <v>129.03</v>
@@ -2821,13 +2807,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>60</v>
-      </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2852,13 +2838,13 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
-        <v>60</v>
-      </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2883,13 +2869,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -2914,13 +2900,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -2945,13 +2931,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>63</v>
-      </c>
-      <c r="C64" t="s">
-        <v>64</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -2980,13 +2966,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>63</v>
-      </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3015,13 +3001,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" t="s">
         <v>62</v>
       </c>
-      <c r="B66" t="s">
-        <v>63</v>
-      </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3050,13 +3036,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3091,13 +3077,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3132,10 +3118,10 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3160,10 +3146,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D70">
         <v>75.375</v>
@@ -3182,10 +3168,10 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D71">
         <v>87.5</v>
@@ -3204,10 +3190,10 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <v>124.25</v>
@@ -3226,10 +3212,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D73">
         <v>150.5</v>
@@ -3248,10 +3234,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74">
         <v>176.75</v>
@@ -3270,10 +3256,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
         <v>75</v>
-      </c>
-      <c r="B75" t="s">
-        <v>76</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3302,10 +3288,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3334,10 +3320,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3366,10 +3352,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3398,10 +3384,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
         <v>80</v>
-      </c>
-      <c r="B79" t="s">
-        <v>81</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3458,10 +3444,10 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3488,10 +3474,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3518,10 +3504,10 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3548,10 +3534,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>

--- a/catalogue print et signalétique.xlsx
+++ b/catalogue print et signalétique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267CA51A-59E8-4065-8B6B-782384DB9E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBF624B-699B-44CA-AB5A-BBABEC1725D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="77">
   <si>
     <t>Colonne A</t>
   </si>
@@ -71,30 +71,6 @@
     <t>Modèle / Référence exacte</t>
   </si>
   <si>
-    <t>Panneaux de chantier
-Panneaux alvéolaires en polypropylène (Akylux) Oeillets aux 4 coins
-Impression quadri
-Portrait ou paysage **</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 60 x 40 cm - épaisseur 3,5 mm ** - Recto</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 60 x 40 cm - épaisseur 3,5 mm ** Recto-verso</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 80 x 60 cm - épaisseur 3,5 mm ** - Recto</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 80 x 60 cm - épaisseur 3,5 mm ** - Recto-verso</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 120 x 80 cm - épaisseur 3,5 mm ** - Recto</t>
-  </si>
-  <si>
-    <t>Panneau de chantier - Format 120 x 80 cm - épaisseur 3,5 mm ** - Recto-verso</t>
-  </si>
-  <si>
     <t>Roll up</t>
   </si>
   <si>
@@ -129,36 +105,6 @@
   </si>
   <si>
     <t>115g recyclé</t>
-  </si>
-  <si>
-    <t>135g couché brillant - Recto</t>
-  </si>
-  <si>
-    <t>170g couché demi mat - Recto</t>
-  </si>
-  <si>
-    <t>250g couché brillant ou demi mat - Recto</t>
-  </si>
-  <si>
-    <t>350g couché demi mat - Recto</t>
-  </si>
-  <si>
-    <t>115g recyclé - Recto</t>
-  </si>
-  <si>
-    <t>135g couché brillant - Recto/verso</t>
-  </si>
-  <si>
-    <t>170g couché demi mat - Recto/verso</t>
-  </si>
-  <si>
-    <t>250g couché brillant ou demi mat - Recto/verso</t>
-  </si>
-  <si>
-    <t>350g couché demi mat - Recto/verso</t>
-  </si>
-  <si>
-    <t>115g recyclé - Recto/verso</t>
   </si>
   <si>
     <t>Flyer A5</t>
@@ -301,6 +247,30 @@
   </si>
   <si>
     <t>Bloc Note collé - Format A4 - 50 Feuilles - 90 Gr Offset</t>
+  </si>
+  <si>
+    <t>Panneaux de chantier Panneaux alvéolaires en polypropylène (Akylux) Oeillets aux 4 coins Impression quadri Portrait ou paysage **</t>
+  </si>
+  <si>
+    <t>Recto-verso</t>
+  </si>
+  <si>
+    <t>Panneau de chantier - Format 60 x 40 cm - épaisseur 3,5 mm</t>
+  </si>
+  <si>
+    <t>Panneau de chantier - Format 80 x 60 cm - épaisseur 3,5 mm</t>
+  </si>
+  <si>
+    <t>Panneau de chantier - Format 120 x 80 cm - épaisseur 3,5 mm</t>
+  </si>
+  <si>
+    <t>Roll-Up Eco</t>
+  </si>
+  <si>
+    <t>Roll-Up Pro</t>
+  </si>
+  <si>
+    <t>350g couché demi mat</t>
   </si>
 </sst>
 </file>
@@ -414,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -431,6 +401,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,7 +741,8 @@
   <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="41.140625" customWidth="1"/>
+    <col min="1" max="1" width="148.85546875" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" customWidth="1"/>
     <col min="3" max="3" width="71.28515625" customWidth="1"/>
     <col min="4" max="8" width="24.140625" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
@@ -813,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -856,11 +830,14 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
+      <c r="A3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3">
@@ -886,11 +863,14 @@
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
+      <c r="A4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
@@ -916,11 +896,14 @@
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
+      <c r="A5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5">
@@ -946,11 +929,14 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
+      <c r="A6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6">
@@ -976,11 +962,14 @@
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
+      <c r="A7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7">
@@ -1006,11 +995,14 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
+      <c r="A8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8">
@@ -1037,10 +1029,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>64.8</v>
@@ -1059,10 +1054,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>93.6</v>
@@ -1081,10 +1079,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>96</v>
@@ -1103,10 +1104,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>141.6</v>
@@ -1125,10 +1129,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1160,10 +1167,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1194,10 +1204,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1228,10 +1241,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1262,10 +1278,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1296,10 +1315,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1330,10 +1352,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1364,10 +1389,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1398,10 +1426,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1432,10 +1463,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1466,10 +1500,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1500,10 +1537,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1534,10 +1574,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1568,10 +1611,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1602,10 +1648,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1636,10 +1685,13 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1670,10 +1722,13 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1704,10 +1759,13 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1738,10 +1796,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1772,10 +1833,13 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1806,13 +1870,13 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1843,13 +1907,13 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1880,13 +1944,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1917,13 +1981,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1954,13 +2018,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1991,13 +2055,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2028,13 +2092,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2065,13 +2129,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2102,13 +2166,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2139,13 +2203,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2176,13 +2240,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2213,13 +2277,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2250,13 +2314,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2287,13 +2351,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2324,13 +2388,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2361,10 +2425,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>70</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2393,10 +2460,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>70</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2425,10 +2495,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2457,10 +2530,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2497,10 +2573,13 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>34</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2537,10 +2616,13 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>35</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2577,10 +2659,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>37</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
       </c>
       <c r="D54">
         <v>31.680000000000003</v>
@@ -2617,10 +2702,13 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
       </c>
       <c r="D55">
         <v>61.600000000000009</v>
@@ -2657,10 +2745,13 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
       </c>
       <c r="D56">
         <v>46.2</v>
@@ -2693,10 +2784,13 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>37</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
       </c>
       <c r="D57">
         <v>31.680000000000003</v>
@@ -2733,10 +2827,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
       </c>
       <c r="D58">
         <v>70.400000000000006</v>
@@ -2771,10 +2868,13 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>39</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
       </c>
       <c r="D59">
         <v>129.03</v>
@@ -2807,13 +2907,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2838,13 +2938,13 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2869,13 +2969,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -2900,13 +3000,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -2931,13 +3031,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -2966,13 +3066,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3001,13 +3101,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3036,13 +3136,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3077,13 +3177,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3118,10 +3218,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3146,10 +3249,13 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
       </c>
       <c r="D70">
         <v>75.375</v>
@@ -3168,10 +3274,13 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>52</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
       </c>
       <c r="D71">
         <v>87.5</v>
@@ -3190,10 +3299,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
       </c>
       <c r="D72">
         <v>124.25</v>
@@ -3212,10 +3324,13 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>54</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
       </c>
       <c r="D73">
         <v>150.5</v>
@@ -3234,10 +3349,13 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
       </c>
       <c r="D74">
         <v>176.75</v>
@@ -3256,10 +3374,13 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3288,10 +3409,13 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="C76" t="s">
+        <v>18</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3320,10 +3444,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>60</v>
+      </c>
+      <c r="C77" t="s">
+        <v>17</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3352,10 +3479,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="C78" t="s">
+        <v>18</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3384,10 +3514,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>63</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3414,10 +3547,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="C80" t="s">
+        <v>17</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3444,10 +3580,13 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>65</v>
+      </c>
+      <c r="C81" t="s">
+        <v>17</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3474,10 +3613,13 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>66</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3504,10 +3646,13 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>67</v>
+      </c>
+      <c r="C83" t="s">
+        <v>17</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3534,10 +3679,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>68</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
